--- a/docs/export/erd.xlsx
+++ b/docs/export/erd.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,137 +535,149 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Draft for review (step 1, revision 2). Source of truth: docs/02-erd.md</t>
+          <t>Implemented in backend/database/migrations and running on Supabase (revision 3). Source of truth: docs/02-erd.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Types</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Supabase PostgreSQL. Schema owned by Laravel migrations.</t>
+          <t>All timestamps are timestamptz (UTC). Every table has created_at/updated_at except votes, otp_codes and audit_logs (created_at only, never updated).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Visitor identity (phone = UID)</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>The phone number is the visitor's UID: normalised to E.164, enforced by the UNIQUE HMAC blind index visitors.phone_hash and used for every lookup. Visitors enter only full name + phone. The numeric id is an internal join key only (so the phone is not copied into other tables and rotating the HMAC secret never breaks relations). Phone and id are never exposed in URLs or API responses. Limit: one phone = one person is an assumption (multiple SIMs / virtual numbers could hold several UIDs).</t>
+          <t>Supabase PostgreSQL. Schema owned by Laravel migrations.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Multi-event model</t>
+          <t>Visitor identity (phone = UID)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Many independent voting events. Each event has its own categories, exhibitors, voting window, on-site rules, registrations/verification, votes, results, display tokens and admin panel.</t>
+          <t>The phone number is the visitor's UID: normalised to E.164, enforced by the UNIQUE HMAC blind index visitors.phone_hash and used for every lookup. Visitors enter only full name + phone. The numeric id is an internal join key only (so the phone is not copied into other tables and rotating the HMAC secret never breaks relations). Phone and id are never exposed in URLs or API responses. Limit: one phone = one person is an assumption (multiple SIMs / virtual numbers could hold several UIDs).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>OTP per event</t>
+          <t>Multi-event model</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Visitor identity is global (one row per phone, de-duplicated for outreach) but OTP verification lives on event_registrations, so it must be confirmed again for every new event.</t>
+          <t>Many independent voting events. Each event has its own categories, exhibitors, voting window, on-site rules, registrations/verification, votes, results, display tokens and admin panel.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Same-event integrity</t>
+          <t>OTP per event</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Composite foreign keys (event_id, ...) guarantee categories, exhibitors, registrations and votes of an event can never point at another event's rows.</t>
+          <t>Visitor identity is global (one row per phone, de-duplicated for outreach) but OTP verification lives on event_registrations, so it must be confirmed again for every new event.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Voting open rule</t>
+          <t>Same-event integrity</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>voting_enabled = true AND (opens_at is null OR now &gt;= opens_at) AND (closes_at is null OR now &lt; closes_at)</t>
+          <t>Composite foreign keys (event_id, ...) guarantee categories, exhibitors, registrations and votes of an event can never point at another event's rows.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>One vote per category</t>
+          <t>Voting open rule</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>UNIQUE (visitor_id, category_id) on votes - enforced by the database (F2, F12). Votes are immutable.</t>
+          <t>voting_enabled = true AND (opens_at is null OR now &gt;= opens_at) AND (closes_at is null OR now &lt; closes_at)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Privacy (F14)</t>
+          <t>One vote per category</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Phone stored encrypted (phone_encrypted) + HMAC-SHA256 blind index (phone_hash) for uniqueness/lookup. RLS enabled with NO policies on every table so the public Supabase API cannot read data; Laravel is the only access path. OTP codes and tokens stored hashed.</t>
+          <t>UNIQUE (visitor_id, category_id) on votes - enforced by the database (F2, F12). Votes are immutable.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Admins</t>
+          <t>Privacy (F14)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>One pool of admins (users); every admin can manage every event. MFA (TOTP) enrolled via two_factor_*.</t>
+          <t>Phone stored encrypted (phone_encrypted) + HMAC-SHA256 blind index (phone_hash) for uniqueness/lookup. RLS enabled with NO policies on every table so the public Supabase API cannot read data; Laravel is the only access path. anon/authenticated roles also have all table privileges revoked. OTP codes and tokens stored hashed.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Framework tables (not listed)</t>
+          <t>Admins</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>personal_access_tokens (Sanctum; visitor + display tokens, bound to one event via abilities), sessions, cache, cache_locks, jobs, failed_jobs - database-backed so the app stays stateless.</t>
+          <t>One pool of admins (users); every admin can manage every event. MFA (TOTP) enrolled via two_factor_*.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Framework tables (not listed)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>personal_access_tokens (Sanctum; visitor + display tokens, bound to one event via abilities), sessions, cache, cache_locks, jobs, failed_jobs - database-backed so the app stays stateless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Not drawn in the picture</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>votes.event_id -&gt; events.id and audit_logs.event_id -&gt; events.id exist (see Relationships tab).</t>
         </is>
@@ -1365,7 +1377,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
@@ -1745,7 +1757,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
@@ -1985,7 +1997,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
@@ -2129,7 +2141,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
@@ -2185,7 +2197,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr"/>
@@ -2297,7 +2309,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr"/>
@@ -2353,7 +2365,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr"/>
@@ -2409,7 +2421,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr"/>
@@ -2613,7 +2625,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
@@ -2704,7 +2716,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Bcrypt/Argon2 hash</t>
+          <t>Bcrypt/Argon2 hash. Admins log in with username + password + TOTP; no email stored</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2761,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr"/>
@@ -2949,7 +2961,7 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr"/>

--- a/docs/export/erd.xlsx
+++ b/docs/export/erd.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>One pool of admins (users); every admin can manage every event. MFA (TOTP) enrolled via two_factor_*.</t>
+          <t>One pool of admins (users); every admin can manage every event. MFA (TOTP, required) stored in app_authentication_secret + recovery codes.</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>two_factor_secret</t>
+          <t>app_authentication_secret</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>TOTP secret, encrypted</t>
+          <t>TOTP secret for the authenticator app, encrypted (Filament MFA)</t>
         </is>
       </c>
     </row>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>two_factor_confirmed_at</t>
+          <t>app_authentication_recovery_codes</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>MFA enrolled</t>
+          <t>One-time recovery codes, encrypted</t>
         </is>
       </c>
     </row>

--- a/docs/export/erd.xlsx
+++ b/docs/export/erd.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constraints &amp; Indexes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tables'!$A$1:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Columns'!$A$1:$F$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relationships'!$A$1:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints &amp; Indexes'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tables'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Columns'!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relationships'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints &amp; Indexes'!$A$1:$D$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Implemented in backend/database/migrations and running on Supabase (revision 3). Source of truth: docs/02-erd.md</t>
+          <t>Implemented in backend/database/migrations and running on Supabase (revision 4). Source of truth: docs/02-erd.md</t>
         </is>
       </c>
     </row>
@@ -602,82 +602,94 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Same-event integrity</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Composite foreign keys (event_id, ...) guarantee categories, exhibitors, registrations and votes of an event can never point at another event's rows.</t>
+          <t>At most 3 categories per event; each exhibitor competes in exactly one category (decision; spec F9 allowed one or more).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Voting open rule</t>
+          <t>Same-event integrity</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>voting_enabled = true AND (opens_at is null OR now &gt;= opens_at) AND (closes_at is null OR now &lt; closes_at)</t>
+          <t>Composite foreign keys (event_id, ...) guarantee categories, exhibitors, registrations and votes of an event can never point at another event's rows.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>One vote per category</t>
+          <t>Voting open rule</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>UNIQUE (visitor_id, category_id) on votes - enforced by the database (F2, F12). Votes are immutable.</t>
+          <t>voting_enabled = true AND (opens_at is null OR now &gt;= opens_at) AND (closes_at is null OR now &lt; closes_at)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Privacy (F14)</t>
+          <t>One vote per category</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Phone stored encrypted (phone_encrypted) + HMAC-SHA256 blind index (phone_hash) for uniqueness/lookup. RLS enabled with NO policies on every table so the public Supabase API cannot read data; Laravel is the only access path. anon/authenticated roles also have all table privileges revoked. OTP codes and tokens stored hashed.</t>
+          <t>UNIQUE (visitor_id, category_id) on votes - enforced by the database (F2, F12). Votes are immutable.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Admins</t>
+          <t>Privacy (F14)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>One pool of admins (users); every admin can manage every event. MFA (TOTP, required) stored in app_authentication_secret + recovery codes.</t>
+          <t>Phone stored encrypted (phone_encrypted) + HMAC-SHA256 blind index (phone_hash) for uniqueness/lookup. RLS enabled with NO policies on every table so the public Supabase API cannot read data; Laravel is the only access path. anon/authenticated roles also have all table privileges revoked. OTP codes and tokens stored hashed.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Framework tables (not listed)</t>
+          <t>Admins</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>personal_access_tokens (Sanctum; visitor + display tokens, bound to one event via abilities), sessions, cache, cache_locks, jobs, failed_jobs - database-backed so the app stays stateless.</t>
+          <t>One pool of admins (users); every admin can manage every event. MFA (TOTP, required) stored in app_authentication_secret + recovery codes.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Framework tables (not listed)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>personal_access_tokens (Sanctum; visitor + display tokens, bound to one event via abilities), sessions, cache, cache_locks, jobs, failed_jobs - database-backed so the app stays stateless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Not drawn in the picture</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>votes.event_id -&gt; events.id and audit_logs.event_id -&gt; events.id exist (see Relationships tab).</t>
         </is>
@@ -694,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -773,41 +785,41 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Per event</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Many-to-many: exhibitor entered in one or more categories of the same event.</t>
+          <t>One row per phone number = the visitor's UID (encrypted + blind index). Identity only - no verification state.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Per event</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>One row per phone number = the visitor's UID (encrypted + blind index). Identity only - no verification state.</t>
+          <t>A visitor's participation in ONE event; holds phone_verified_at, i.e. the per-event OTP confirmation.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>otp_codes</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -817,14 +829,14 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>A visitor's participation in ONE event; holds phone_verified_at, i.e. the per-event OTP confirmation.</t>
+          <t>Hashed one-time codes, belonging to an event registration.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>otp_codes</t>
+          <t>votes</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -834,63 +846,46 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Hashed one-time codes, belonging to an event registration.</t>
+          <t>One row per cast vote; immutable; unique per visitor + category.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>votes</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Per event</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>One row per cast vote; immutable; unique per visitor + category.</t>
+          <t>Admins (Makerspace staff). Not visitors.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>audit_logs</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global / per event</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Admins (Makerspace staff). Not visitors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>audit_logs</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Global / per event</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
           <t>Append-only log of sensitive admin actions (reset, exports, settings).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C11"/>
+  <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -901,7 +896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1648,21 +1643,29 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>category_id</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>The one category it competes in: (event_id, category_id) -&gt; categories(event_id, id)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1672,12 +1675,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>short_description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
@@ -1686,11 +1689,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Shown on the voting card</t>
-        </is>
-      </c>
+      <c r="F28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1700,23 +1699,23 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>photo_path</t>
+          <t>short_description</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Object key in Supabase Storage (S3-compatible); API builds the public URL</t>
+          <t>Shown on the voting card</t>
         </is>
       </c>
     </row>
@@ -1728,21 +1727,25 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>photo_path</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Object key in Supabase Storage (S3-compatible); API builds the public URL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -1752,67 +1755,59 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Soft delete; hard delete blocked once votes exist</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>exhibitors</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Part of both composite FKs</t>
+          <t>Soft delete; hard delete blocked once votes exist</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1822,7 +1817,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>PK, FK</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1830,33 +1825,25 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>(event_id, category_id) -&gt; categories(event_id, id)</t>
-        </is>
-      </c>
+      <c r="F33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>exhibitor_id</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>PK, FK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -1864,7 +1851,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>(event_id, exhibitor_id) -&gt; exhibitors(event_id, id)</t>
+          <t>Latest full name from a VERIFIED registration (outreach list)</t>
         </is>
       </c>
     </row>
@@ -1876,25 +1863,25 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>phone_encrypted</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>E.164 number, Laravel encrypted cast (app key). Admin context only</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1904,15 +1891,19 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>phone_hash</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr"/>
+          <t>char(64)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -1920,7 +1911,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Latest full name from a VERIFIED registration (outreach list)</t>
+          <t>HMAC-SHA256 of the E.164 number with a dedicated secret - blind index</t>
         </is>
       </c>
     </row>
@@ -1932,45 +1923,41 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>phone_encrypted</t>
+          <t>created_at / updated_at</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>E.164 number, Laravel encrypted cast (app key). Admin context only</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>phone_hash</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>char(64)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -1978,35 +1965,39 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>HMAC-SHA256 of the E.164 number with a dedicated secret - blind index</t>
-        </is>
-      </c>
+      <c r="F38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>created_at / updated_at</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; events.id</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -2016,7 +2007,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>visitor_id</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2026,7 +2017,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -2034,7 +2025,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; visitors.id</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -2044,19 +2039,15 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr"/>
       <c r="E41" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -2064,7 +2055,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>-&gt; events.id</t>
+          <t>Full name entered for this event; copied to visitors.full_name only after verification</t>
         </is>
       </c>
     </row>
@@ -2076,27 +2067,23 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>visitor_id</t>
+          <t>phone_verified_at</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>-&gt; visitors.id</t>
+          <t>Set when THIS event's OTP is verified (F6)</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2095,23 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>registered_ip</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>inet</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Full name entered for this event; copied to visitors.full_name only after verification</t>
+          <t>Audit</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2123,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>phone_verified_at</t>
+          <t>created_at / updated_at</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2150,63 +2137,67 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Set when THIS event's OTP is verified (F6)</t>
-        </is>
-      </c>
+      <c r="F44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>otp_codes</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>registered_ip</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>inet</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Audit</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>otp_codes</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>created_at / updated_at</t>
+          <t>event_registration_id</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; event_registrations.id ON DELETE CASCADE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -2216,25 +2207,25 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>code_hash</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr"/>
       <c r="E47" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Hash of the 6-digit code; plain code never stored</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2244,19 +2235,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>event_registration_id</t>
+          <t>expires_at</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr"/>
       <c r="E48" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -2264,7 +2251,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>-&gt; event_registrations.id ON DELETE CASCADE</t>
+          <t>TTL from events.otp_ttl_seconds</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2263,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>code_hash</t>
+          <t>attempts</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
@@ -2292,7 +2279,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Hash of the 6-digit code; plain code never stored</t>
+          <t>Failed verifications; invalidated at events.otp_max_attempts</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2291,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>expires_at</t>
+          <t>consumed_at</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2315,12 +2302,12 @@
       <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>TTL from events.otp_ttl_seconds</t>
+          <t>Single use</t>
         </is>
       </c>
     </row>
@@ -2332,23 +2319,23 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>attempts</t>
+          <t>ip</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>inet</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Failed verifications; invalidated at events.otp_max_attempts</t>
+          <t>Requesting IP (rate limit / audit)</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2347,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>consumed_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -2371,66 +2358,70 @@
       <c r="D52" s="7" t="inlineStr"/>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Single use</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>otp_codes</t>
+          <t>votes</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>ip</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>inet</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Requesting IP (rate limit / audit)</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>otp_codes</t>
+          <t>votes</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Part of both composite FKs</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -2440,7 +2431,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>visitor_id</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -2450,7 +2441,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -2458,7 +2449,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>(event_id, visitor_id) -&gt; event_registrations</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -2468,7 +2463,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>category_id</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -2488,7 +2483,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Part of both composite FKs</t>
+          <t>(event_id, category_id, exhibitor_id) -&gt; exhibitors(event_id, category_id, id)</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2495,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>visitor_id</t>
+          <t>exhibitor_id</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -2518,11 +2513,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>(event_id, visitor_id) -&gt; event_registrations</t>
-        </is>
-      </c>
+      <c r="F57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -2532,27 +2523,23 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>ip</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>inet</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr"/>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>(event_id, category_id, exhibitor_id) -&gt; category_exhibitor</t>
+          <t>Audit</t>
         </is>
       </c>
     </row>
@@ -2564,19 +2551,15 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>exhibitor_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr"/>
       <c r="E59" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -2587,48 +2570,52 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>votes</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>ip</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>inet</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Audit</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>votes</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>username</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr"/>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -2644,25 +2631,25 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>password</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr"/>
       <c r="E62" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Bcrypt/Argon2 hash. Admins log in with username + password + TOTP; no email stored</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -2672,25 +2659,25 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>app_authentication_secret</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr"/>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>TOTP secret for the authenticator app, encrypted (Filament MFA)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -2700,71 +2687,75 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>password</t>
+          <t>app_authentication_recovery_codes</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr"/>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Bcrypt/Argon2 hash. Admins log in with username + password + TOTP; no email stored</t>
+          <t>One-time recovery codes, encrypted</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>audit_logs</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>app_authentication_secret</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>TOTP secret for the authenticator app, encrypted (Filament MFA)</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>audit_logs</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>app_authentication_recovery_codes</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2772,7 +2763,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>One-time recovery codes, encrypted</t>
+          <t>-&gt; users.id</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2775,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -2794,15 +2785,19 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; events.id; null for global actions (e.g. login)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -2812,27 +2807,23 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr"/>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>-&gt; users.id</t>
+          <t>e.g. votes.reset, visitors.export</t>
         </is>
       </c>
     </row>
@@ -2844,19 +2835,15 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr"/>
       <c r="E69" s="7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2864,7 +2851,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>-&gt; events.id; null for global actions (e.g. login)</t>
+          <t>Details (old/new values, counts)</t>
         </is>
       </c>
     </row>
@@ -2876,25 +2863,21 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>ip</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>inet</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>e.g. votes.reset, visitors.export</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -2904,76 +2887,24 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr"/>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Details (old/new values, counts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>audit_logs</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>ip</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>inet</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>audit_logs</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr"/>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F73"/>
+  <autoFilter ref="A1:F71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2984,7 +2915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3190,12 +3121,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -3205,29 +3136,29 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>(event_id, category_id) -&gt; categories(event_id, id)</t>
+          <t>event_registrations.visitor_id</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Same-event guarantee</t>
+          <t>One visitor, many events</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>exhibitors</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>otp_codes</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -3237,7 +3168,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>(event_id, exhibitor_id) -&gt; exhibitors(event_id, id)</t>
+          <t>otp_codes.event_registration_id</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3247,19 +3178,19 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Same-event guarantee</t>
+          <t>OTPs are per event registration</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>votes</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -3269,7 +3200,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>event_registrations.visitor_id</t>
+          <t>(event_id, visitor_id) -&gt; event_registrations(event_id, visitor_id)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -3279,19 +3210,19 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>One visitor, many events</t>
+          <t>Voter must be registered for that event</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>categories</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>otp_codes</t>
+          <t>exhibitors</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -3301,24 +3232,24 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>otp_codes.event_registration_id</t>
+          <t>(event_id, category_id) -&gt; categories(event_id, id)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>OTPs are per event registration</t>
+          <t>Each exhibitor competes in exactly one category of its own event</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>exhibitors</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -3333,24 +3264,24 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>(event_id, visitor_id) -&gt; event_registrations(event_id, visitor_id)</t>
+          <t>(event_id, category_id, exhibitor_id) -&gt; exhibitors(event_id, category_id, id)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RESTRICT</t>
+          <t>RESTRICT (delete + update)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Voter must be registered for that event</t>
+          <t>Vote only for an exhibitor of that category; exhibitor with votes cannot change category</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -3365,7 +3296,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>(event_id, category_id, exhibitor_id) -&gt; category_exhibitor</t>
+          <t>votes.visitor_id</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -3375,29 +3306,29 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Vote only for an exhibitor entered in that category of that event</t>
+          <t>Votes linked to the visitor (F14)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>votes</t>
+          <t>audit_logs</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>1 : N</t>
+          <t>1 : 0..N</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>votes.visitor_id</t>
+          <t>audit_logs.user_id</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3407,44 +3338,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Votes linked to the visitor (F14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>audit_logs</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>1 : 0..N</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>audit_logs.user_id</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
           <t>Who performed the action</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3455,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3599,29 +3498,29 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>PRIMARY KEY</t>
+          <t>UNIQUE</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>(category_id, exhibitor_id)</t>
+          <t>(phone_hash)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>An exhibitor is entered in a category once</t>
+          <t>One visitor per phone number (blind index)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3631,85 +3530,85 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>(event_id, category_id, exhibitor_id)</t>
+          <t>(event_id, visitor_id)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Target of the votes composite FK</t>
+          <t>One registration per visitor per event; target of the votes FK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>otp_codes</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>FOREIGN KEY</t>
+          <t>INDEX</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>(event_id, category_id) -&gt; categories(event_id, id)</t>
+          <t>(event_registration_id, created_at DESC)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Category and exhibitor must be in the same event</t>
+          <t>Find the latest active code</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>category_exhibitor</t>
+          <t>votes</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FOREIGN KEY</t>
+          <t>UNIQUE</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>(event_id, exhibitor_id) -&gt; exhibitors(event_id, id)</t>
+          <t>(visitor_id, category_id)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Category and exhibitor must be in the same event</t>
+          <t>ONE VOTE PER CATEGORY per verified phone (F2, F12) - holds under concurrency, retries and multiple instances</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>exhibitors</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>FOREIGN KEY</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>(phone_hash)</t>
+          <t>(event_id, category_id) -&gt; categories(event_id, id)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>One visitor per phone number (blind index)</t>
+          <t>Category must belong to the exhibitor's own event</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>exhibitors</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3719,56 +3618,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>(event_id, visitor_id)</t>
+          <t>(event_id, category_id, id)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>One registration per visitor per event; target of the votes FK</t>
+          <t>Target of the votes composite FK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>otp_codes</t>
+          <t>votes</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>INDEX</t>
+          <t>FOREIGN KEY</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>(event_registration_id, created_at DESC)</t>
+          <t>(event_id, category_id, exhibitor_id) -&gt; exhibitors(event_id, category_id, id) ON UPDATE RESTRICT</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Find the latest active code</t>
+          <t>Vote must match the exhibitor's category; blocks moving an exhibitor that has votes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>votes</t>
+          <t>categories</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>MODEL RULE</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>(visitor_id, category_id)</t>
+          <t>max 3 per event (voting.max_categories_per_event)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>ONE VOTE PER CATEGORY per verified phone (F2, F12) - holds under concurrency, retries and multiple instances</t>
+          <t>Spec: 3 award categories</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3684,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>(event_id, category_id, exhibitor_id) -&gt; category_exhibitor</t>
+          <t>(event_id, visitor_id) -&gt; event_registrations</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Exhibitor must be entered in that category of that event; blocks un-assigning after votes</t>
+          <t>Voter must be registered for that event (verified state checked in the vote transaction)</t>
         </is>
       </c>
     </row>
@@ -3802,84 +3701,62 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>FOREIGN KEY</t>
+          <t>INDEX</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>(event_id, visitor_id) -&gt; event_registrations</t>
+          <t>(event_id, category_id, exhibitor_id)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Voter must be registered for that event (verified state checked in the vote transaction)</t>
+          <t>Cheap tally queries (COUNT ... GROUP BY)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>votes</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>INDEX</t>
+          <t>UNIQUE</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>(event_id, category_id, exhibitor_id)</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Cheap tally queries (COUNT ... GROUP BY)</t>
-        </is>
-      </c>
+          <t>(username)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>ALL tables</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>SECURITY</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>(username)</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>ALL tables</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>SECURITY</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
           <t>Row Level Security ENABLED, no policies</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Supabase public (anon) API returns nothing; Laravel uses the privileged DB role</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D19"/>
+  <autoFilter ref="A1:D18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/export/erd.xlsx
+++ b/docs/export/erd.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tables'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Columns'!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Columns'!$A$1:$F$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relationships'!$A$1:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints &amp; Indexes'!$A$1:$D$18</definedName>
   </definedNames>
@@ -535,7 +535,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Implemented in backend/database/migrations and running on Supabase (revision 4). Source of truth: docs/02-erd.md</t>
+          <t>Implemented in backend/database/migrations and running on Supabase (revision 5: Wi-Fi only). Source of truth: docs/02-erd.md</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>access_mode</t>
+          <t>allowed_cidrs</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>ip | geo | either | both (F11)</t>
+          <t>Venue public IP ranges, IPv4 AND IPv6, e.g. ["203.0.113.0/24", "2001:db8:1::/48"]. Venue visitors share them (Wi-Fi NAT)</t>
         </is>
       </c>
     </row>
@@ -1199,23 +1199,23 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>allowed_cidrs</t>
+          <t>venue_wifi_name</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Venue public IP ranges, IPv4 AND IPv6, e.g. ["203.0.113.0/24", "2001:db8:1::/48"]. Venue visitors share them (Wi-Fi NAT)</t>
+          <t>Wi-Fi name shown on the 'No access' page, e.g. MC2026-Guest</t>
         </is>
       </c>
     </row>
@@ -1227,23 +1227,23 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>geofence</t>
+          <t>otp_ttl_seconds</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>{"lat":..,"lng":..,"radius_m":..}. Optional backup to the IP check</t>
+          <t>Default 300</t>
         </is>
       </c>
     </row>
@@ -1255,23 +1255,23 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>venue_wifi_name</t>
+          <t>otp_max_attempts</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Wi-Fi name shown on the 'No access' page, e.g. MC2026-Guest</t>
+          <t>Default 5 - wrong-code attempts before the code is invalidated</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>otp_ttl_seconds</t>
+          <t>otp_resend_cooldown_seconds</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Default 300</t>
+          <t>Default 60</t>
         </is>
       </c>
     </row>
@@ -1311,77 +1311,81 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>otp_max_attempts</t>
+          <t>created_at / updated_at</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Default 5 - wrong-code attempts before the code is invalidated</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>categories</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>otp_resend_cooldown_seconds</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Default 60</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>categories</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>created_at / updated_at</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; events.id</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1391,25 +1395,25 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>slug</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>UNIQUE per event: (event_id, slug)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1419,29 +1423,21 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>-&gt; events.id</t>
-        </is>
-      </c>
+      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1451,25 +1447,21 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>slug</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>UNIQUE per event: (event_id, slug)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1479,12 +1471,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
@@ -1493,7 +1485,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Display order</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1503,67 +1499,75 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Inactive categories are hidden and cannot receive votes</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t>exhibitors</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Display order</t>
-        </is>
-      </c>
+      <c r="F23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t>exhibitors</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -1571,7 +1575,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Inactive categories are hidden and cannot receive votes</t>
+          <t>-&gt; events.id</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1587,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>category_id</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1601,7 +1605,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>The one category it competes in: (event_id, category_id) -&gt; categories(event_id, id)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1611,29 +1619,21 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>-&gt; events.id</t>
-        </is>
-      </c>
+      <c r="F26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1643,19 +1643,15 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>short_description</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -1663,7 +1659,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>The one category it competes in: (event_id, category_id) -&gt; categories(event_id, id)</t>
+          <t>Shown on the voting card</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1671,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>photo_path</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1686,10 +1682,14 @@
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Object key in Supabase Storage (S3-compatible); API builds the public URL</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>short_description</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
@@ -1713,11 +1713,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Shown on the voting card</t>
-        </is>
-      </c>
+      <c r="F29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1727,12 +1723,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>photo_path</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
@@ -1743,27 +1739,31 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Object key in Supabase Storage (S3-compatible); API builds the public URL</t>
+          <t>Soft delete; hard delete blocked once votes exist</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>exhibitors</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -1774,28 +1774,28 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>exhibitors</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Soft delete; hard delete blocked once votes exist</t>
+          <t>Latest full name from a VERIFIED registration (outreach list)</t>
         </is>
       </c>
     </row>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>phone_encrypted</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>E.164 number, Laravel encrypted cast (app key). Admin context only</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1835,15 +1835,19 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>phone_hash</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr"/>
+          <t>char(64)</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Latest full name from a VERIFIED registration (outreach list)</t>
+          <t>HMAC-SHA256 of the E.164 number with a dedicated secret - blind index</t>
         </is>
       </c>
     </row>
@@ -1863,45 +1867,41 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>phone_encrypted</t>
+          <t>created_at / updated_at</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>E.164 number, Laravel encrypted cast (app key). Admin context only</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>phone_hash</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>char(64)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1909,35 +1909,39 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>HMAC-SHA256 of the E.164 number with a dedicated secret - blind index</t>
-        </is>
-      </c>
+      <c r="F36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>event_registrations</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>created_at / updated_at</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; events.id</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1947,7 +1951,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>visitor_id</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -1957,7 +1961,7 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -1965,7 +1969,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; visitors.id</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -1975,19 +1983,15 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr"/>
       <c r="E39" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -1995,7 +1999,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>-&gt; events.id</t>
+          <t>Full name entered for this event; copied to visitors.full_name only after verification</t>
         </is>
       </c>
     </row>
@@ -2007,27 +2011,23 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>visitor_id</t>
+          <t>phone_verified_at</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr"/>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>-&gt; visitors.id</t>
+          <t>Set when THIS event's OTP is verified (F6)</t>
         </is>
       </c>
     </row>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>registered_ip</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>inet</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Full name entered for this event; copied to visitors.full_name only after verification</t>
+          <t>Audit</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>phone_verified_at</t>
+          <t>created_at / updated_at</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2081,63 +2081,67 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Set when THIS event's OTP is verified (F6)</t>
-        </is>
-      </c>
+      <c r="F42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>otp_codes</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>registered_ip</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>inet</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Audit</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>event_registrations</t>
+          <t>otp_codes</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>created_at / updated_at</t>
+          <t>event_registration_id</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; event_registrations.id ON DELETE CASCADE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -2147,25 +2151,25 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>code_hash</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Hash of the 6-digit code; plain code never stored</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -2175,19 +2179,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>event_registration_id</t>
+          <t>expires_at</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr"/>
       <c r="E46" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>-&gt; event_registrations.id ON DELETE CASCADE</t>
+          <t>TTL from events.otp_ttl_seconds</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>code_hash</t>
+          <t>attempts</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Hash of the 6-digit code; plain code never stored</t>
+          <t>Failed verifications; invalidated at events.otp_max_attempts</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>expires_at</t>
+          <t>consumed_at</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -2246,12 +2246,12 @@
       <c r="D48" s="7" t="inlineStr"/>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>TTL from events.otp_ttl_seconds</t>
+          <t>Single use</t>
         </is>
       </c>
     </row>
@@ -2263,23 +2263,23 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>attempts</t>
+          <t>ip</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>inet</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Failed verifications; invalidated at events.otp_max_attempts</t>
+          <t>Requesting IP (rate limit / audit)</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>consumed_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2302,66 +2302,70 @@
       <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Single use</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>otp_codes</t>
+          <t>votes</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>ip</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>inet</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Requesting IP (rate limit / audit)</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>otp_codes</t>
+          <t>votes</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Part of both composite FKs</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -2371,7 +2375,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>visitor_id</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -2381,7 +2385,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -2389,7 +2393,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>(event_id, visitor_id) -&gt; event_registrations</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2399,7 +2407,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>category_id</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -2419,7 +2427,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Part of both composite FKs</t>
+          <t>(event_id, category_id, exhibitor_id) -&gt; exhibitors(event_id, category_id, id)</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2439,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>visitor_id</t>
+          <t>exhibitor_id</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -2449,11 +2457,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>(event_id, visitor_id) -&gt; event_registrations</t>
-        </is>
-      </c>
+      <c r="F55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -2463,27 +2467,23 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>ip</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>inet</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr"/>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>(event_id, category_id, exhibitor_id) -&gt; exhibitors(event_id, category_id, id)</t>
+          <t>Audit</t>
         </is>
       </c>
     </row>
@@ -2495,19 +2495,15 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>exhibitor_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr"/>
       <c r="E57" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -2518,48 +2514,52 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>votes</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>ip</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>inet</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Audit</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>votes</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>username</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr"/>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
           <t>no</t>
@@ -2575,25 +2575,25 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>password</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr"/>
       <c r="E60" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Bcrypt/Argon2 hash. Admins log in with username + password + TOTP; no email stored</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -2603,25 +2603,25 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>app_authentication_secret</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr"/>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>TOTP secret for the authenticator app, encrypted (Filament MFA)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -2631,71 +2631,75 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>password</t>
+          <t>app_authentication_recovery_codes</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr"/>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Bcrypt/Argon2 hash. Admins log in with username + password + TOTP; no email stored</t>
+          <t>One-time recovery codes, encrypted</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>audit_logs</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>app_authentication_secret</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>TOTP secret for the authenticator app, encrypted (Filament MFA)</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>audit_logs</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>app_authentication_recovery_codes</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2703,7 +2707,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>One-time recovery codes, encrypted</t>
+          <t>-&gt; users.id</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2719,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -2725,15 +2729,19 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; events.id; null for global actions (e.g. login)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -2743,27 +2751,23 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr"/>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>-&gt; users.id</t>
+          <t>e.g. votes.reset, visitors.export</t>
         </is>
       </c>
     </row>
@@ -2775,19 +2779,15 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr"/>
       <c r="E67" s="7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>-&gt; events.id; null for global actions (e.g. login)</t>
+          <t>Details (old/new values, counts)</t>
         </is>
       </c>
     </row>
@@ -2807,25 +2807,21 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>ip</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>inet</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr"/>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>e.g. votes.reset, visitors.export</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -2835,76 +2831,24 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr"/>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Details (old/new values, counts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>audit_logs</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>ip</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>inet</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr"/>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>audit_logs</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F71"/>
+  <autoFilter ref="A1:F69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
